--- a/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="367">
   <si>
     <t>Result</t>
   </si>
@@ -1088,6 +1088,156 @@
   </si>
   <si>
     <t>Thu Jul 09 16:49:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:47:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:49:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:51:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:52:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:52:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:53:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:54:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:55:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:57:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:58:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:58:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:59:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:00:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:00:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:01:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:02:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:02:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:03:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:04:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:04:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:05:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:06:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:07:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:08:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:09:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:09:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:10:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:12:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:13:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:14:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:15:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:17:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:18:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:19:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:20:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:21:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:21:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:22:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:22:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 18:52:15 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="26">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>62</v>
@@ -1646,7 +1796,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s" s="26">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>62</v>
@@ -1712,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1768,7 +1918,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1824,7 +1974,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1880,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>277</v>
+        <v>366</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1943,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>33</v>
@@ -1964,7 +2114,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>34</v>
@@ -1991,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>29</v>
@@ -2014,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>30</v>
@@ -2037,7 +2187,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>31</v>
@@ -2060,7 +2210,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>32</v>
@@ -2083,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s" s="1">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>44</v>
@@ -2106,7 +2256,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s" s="1">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>45</v>
@@ -2129,7 +2279,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s" s="1">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
@@ -2195,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>37</v>
@@ -2221,7 +2371,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>40</v>
@@ -2241,7 +2391,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>41</v>
@@ -2261,7 +2411,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>42</v>
@@ -2284,7 +2434,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>22</v>
@@ -2307,7 +2457,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>23</v>
@@ -2330,7 +2480,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s" s="1">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>24</v>
@@ -2357,7 +2507,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s" s="1">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>39</v>
@@ -2435,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="16">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
@@ -2512,7 +2662,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="16">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
@@ -2589,7 +2739,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="16">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>51</v>
@@ -2666,7 +2816,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="16">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
@@ -2743,7 +2893,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="6">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
@@ -2820,7 +2970,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="6">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>13</v>
@@ -2877,7 +3027,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2946,7 +3096,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>56</v>
@@ -3015,7 +3165,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>57</v>
@@ -3080,7 +3230,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>300</v>
+        <v>345</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -3136,7 +3286,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>301</v>
+        <v>347</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
